--- a/data/ams_weekly_data/Nexlev/ads_report_week18.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week18.xlsx
@@ -6951,7 +6951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7113,10 +7113,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2365.666666666667</v>
+        <v>2366</v>
       </c>
       <c r="E5" t="n">
-        <v>7.333333333333333</v>
+        <v>7</v>
       </c>
       <c r="F5" t="n">
         <v>209.4666666666667</v>
@@ -7146,10 +7146,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2365.666666666667</v>
+        <v>2366</v>
       </c>
       <c r="E6" t="n">
-        <v>7.333333333333333</v>
+        <v>7</v>
       </c>
       <c r="F6" t="n">
         <v>209.4666666666667</v>
@@ -7179,10 +7179,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2365.666666666667</v>
+        <v>2366</v>
       </c>
       <c r="E7" t="n">
-        <v>7.333333333333333</v>
+        <v>7</v>
       </c>
       <c r="F7" t="n">
         <v>209.4666666666667</v>
@@ -7212,7 +7212,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>555.5</v>
+        <v>556</v>
       </c>
       <c r="E8" t="n">
         <v>12</v>
@@ -7245,7 +7245,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>555.5</v>
+        <v>556</v>
       </c>
       <c r="E9" t="n">
         <v>12</v>
@@ -7311,19 +7311,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>5317</v>
+        <v>2496</v>
       </c>
       <c r="E11" t="n">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="F11" t="n">
-        <v>3584</v>
+        <v>1682.597684333414</v>
       </c>
       <c r="G11" t="n">
-        <v>5413.56</v>
+        <v>2541.53</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -7335,28 +7335,28 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nex_HnK_SBV_KT_MR-01_B0CYSLCRQS_Phrase &amp; Exact</t>
+          <t>Nex_HnK_SBV_KT_MR-01_B0CYSLCRQS_BCG_Phrase &amp; Exact_Reel</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1819</v>
+        <v>2821</v>
       </c>
       <c r="E12" t="n">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="F12" t="n">
-        <v>830.72</v>
+        <v>1901.402315666586</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>2872.03</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -7368,22 +7368,22 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nex_HnK_SBV_KT_MR-02_B0DCK7ZH5P_BCG_Phrase &amp; Exact - Reel</t>
+          <t>Nex_HnK_SBV_KT_MR-01_B0CYSLCRQS_Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>656</v>
+        <v>1819</v>
       </c>
       <c r="E13" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F13" t="n">
-        <v>714.14</v>
+        <v>830.72</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -7401,28 +7401,28 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nex_HnK_SBV_KT_SC-05_B0F43P6D23_BCG_Phrase &amp; Exact_Reel</t>
+          <t>Nex_HnK_SBV_KT_MR-02_B0DCK7ZH5P_BCG_Phrase &amp; Exact - Reel</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1900.333333333333</v>
+        <v>656</v>
       </c>
       <c r="E14" t="n">
-        <v>46.33333333333334</v>
+        <v>32</v>
       </c>
       <c r="F14" t="n">
-        <v>1277.046666666667</v>
+        <v>714.14</v>
       </c>
       <c r="G14" t="n">
-        <v>1881.073333333333</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -7439,23 +7439,23 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1900.333333333333</v>
+        <v>5701</v>
       </c>
       <c r="E15" t="n">
-        <v>46.33333333333334</v>
+        <v>139</v>
       </c>
       <c r="F15" t="n">
-        <v>1277.046666666667</v>
+        <v>3831.14</v>
       </c>
       <c r="G15" t="n">
-        <v>1881.073333333333</v>
+        <v>5643.22</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -7467,28 +7467,28 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nex_HnK_SBV_KT_SC-05_B0F43P6D23_BCG_Phrase &amp; Exact_Reel</t>
+          <t>Nex_HnK_SBV_KT_ST-01_B0DVC7VJP1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1900.333333333333</v>
+        <v>1353</v>
       </c>
       <c r="E16" t="n">
-        <v>46.33333333333334</v>
+        <v>17</v>
       </c>
       <c r="F16" t="n">
-        <v>1277.046666666667</v>
+        <v>379.01</v>
       </c>
       <c r="G16" t="n">
-        <v>1881.073333333333</v>
+        <v>4999.15</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -7500,28 +7500,28 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nex_HnK_SBV_KT_ST-01_B0DVC7VJP1</t>
+          <t>Nex_HnK_SB_KT_GS-02/05_B0CDPMX152_B0D383WQPB</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0CDPMX152</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1353</v>
+        <v>155292</v>
       </c>
       <c r="E17" t="n">
-        <v>17</v>
+        <v>206</v>
       </c>
       <c r="F17" t="n">
-        <v>379.01</v>
+        <v>4721.610000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>4999.15</v>
+        <v>3429.66</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -7533,28 +7533,28 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nex_HnK_SB_KT_GS-02/05_B0CDPMX152_B0D383WQPB</t>
+          <t>Nex_HnK_SB_KT_SC-04_B0DNJS23HS_Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0CDPMX152</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>51764</v>
+        <v>35718</v>
       </c>
       <c r="E18" t="n">
-        <v>68.66666666666667</v>
+        <v>33</v>
       </c>
       <c r="F18" t="n">
-        <v>1573.87</v>
+        <v>321.93</v>
       </c>
       <c r="G18" t="n">
-        <v>1143.22</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -7566,28 +7566,28 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nex_HnK_SB_KT_GS-02/05_B0CDPMX152_B0D383WQPB</t>
+          <t>Nex_HnK_SB_KT_VC-01/VC-02/VC-05_BCG_Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>51764</v>
+        <v>1514</v>
       </c>
       <c r="E19" t="n">
-        <v>68.66666666666667</v>
+        <v>6</v>
       </c>
       <c r="F19" t="n">
-        <v>1573.87</v>
+        <v>58.24</v>
       </c>
       <c r="G19" t="n">
-        <v>1143.22</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -7599,28 +7599,28 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nex_HnK_SB_KT_GS-02/05_B0CDPMX152_B0D383WQPB</t>
+          <t>Nex_HnK_SB_KT_VC-01/VC-02/VC-05_BCG_Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0D845B2DG</t>
+          <t>B0DCK56Q85</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>51764</v>
+        <v>1514</v>
       </c>
       <c r="E20" t="n">
-        <v>68.66666666666667</v>
+        <v>6</v>
       </c>
       <c r="F20" t="n">
-        <v>1573.87</v>
+        <v>58.24</v>
       </c>
       <c r="G20" t="n">
-        <v>1143.22</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -7632,22 +7632,22 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nex_HnK_SB_KT_SC-04_B0DNJS23HS_Phrase &amp; Exact</t>
+          <t>Nex_HnK_SB_KT_VC-01/VC-02/VC-05_BCG_Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>35718</v>
+        <v>1514</v>
       </c>
       <c r="E21" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="F21" t="n">
-        <v>321.93</v>
+        <v>58.24</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -7665,22 +7665,22 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nex_HnK_SB_KT_VC-01/VC-02/VC-05_BCG_Phrase &amp; Exact</t>
+          <t>Nex_Hnk_SBV_KT_ST-01_B0DVC7VJP1_Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1514</v>
+        <v>1234</v>
       </c>
       <c r="E22" t="n">
-        <v>5.666666666666667</v>
+        <v>39</v>
       </c>
       <c r="F22" t="n">
-        <v>58.24</v>
+        <v>572.49</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -7698,28 +7698,28 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nex_HnK_SB_KT_VC-01/VC-02/VC-05_BCG_Phrase &amp; Exact</t>
+          <t>Nexlev - Steam Cleaner - SB - KT - Phrase/Exact</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0DCK56Q85</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1514</v>
+        <v>27768</v>
       </c>
       <c r="E23" t="n">
-        <v>5.666666666666667</v>
+        <v>276</v>
       </c>
       <c r="F23" t="n">
-        <v>58.24</v>
+        <v>8409.512359492419</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>25554.18581175094</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -7731,28 +7731,28 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nex_HnK_SB_KT_VC-01/VC-02/VC-05_BCG_Phrase &amp; Exact</t>
+          <t>Nexlev - Steam Cleaner - SB - KT - Phrase/Exact</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1514</v>
+        <v>19186</v>
       </c>
       <c r="E24" t="n">
-        <v>5.666666666666667</v>
+        <v>191</v>
       </c>
       <c r="F24" t="n">
-        <v>58.24</v>
+        <v>5810.422471601136</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>17656.26936934909</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -7764,28 +7764,28 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nex_Hnk_SBV_KT_ST-01_B0DVC7VJP1_Phrase &amp; Exact</t>
+          <t>Nexlev - Steam Cleaner - SB - KT - Phrase/Exact</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1234</v>
+        <v>18885</v>
       </c>
       <c r="E25" t="n">
-        <v>39</v>
+        <v>191</v>
       </c>
       <c r="F25" t="n">
-        <v>572.49</v>
+        <v>5703.245168906446</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>19524.30481889997</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -7797,28 +7797,28 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nexlev - Steam Cleaner - SB - KT - Phrase/Exact</t>
+          <t>Nexlev -B0DM6BB3VT-Calf Massager-SBV -KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DM6BB3VT</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>21946</v>
+        <v>6312</v>
       </c>
       <c r="E26" t="n">
-        <v>219.3333333333333</v>
+        <v>259</v>
       </c>
       <c r="F26" t="n">
-        <v>6641.06</v>
+        <v>2948.071957926474</v>
       </c>
       <c r="G26" t="n">
-        <v>20911.58666666667</v>
+        <v>15263.97504064594</v>
       </c>
       <c r="H26" t="n">
-        <v>7.333333333333333</v>
+        <v>6</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -7830,28 +7830,28 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nexlev - Steam Cleaner - SB - KT - Phrase/Exact</t>
+          <t>Nexlev -B0DM6BB3VT-Calf Massager-SBV -KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DVSZ2VVJ</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>21946</v>
+        <v>2248</v>
       </c>
       <c r="E27" t="n">
-        <v>219.3333333333333</v>
+        <v>92</v>
       </c>
       <c r="F27" t="n">
-        <v>6641.06</v>
+        <v>1050.099734116108</v>
       </c>
       <c r="G27" t="n">
-        <v>20911.58666666667</v>
+        <v>5437.00980182688</v>
       </c>
       <c r="H27" t="n">
-        <v>7.333333333333333</v>
+        <v>2</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -7863,28 +7863,28 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nexlev - Steam Cleaner - SB - KT - Phrase/Exact</t>
+          <t>Nexlev -B0DM6BB3VT-Calf Massager-SBV -KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0FPGDVVCX</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>21946</v>
+        <v>5015</v>
       </c>
       <c r="E28" t="n">
-        <v>219.3333333333333</v>
+        <v>205</v>
       </c>
       <c r="F28" t="n">
-        <v>6641.06</v>
+        <v>2342.588307957418</v>
       </c>
       <c r="G28" t="n">
-        <v>20911.58666666667</v>
+        <v>12129.01515752718</v>
       </c>
       <c r="H28" t="n">
-        <v>7.333333333333333</v>
+        <v>4</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nexlev -B0DM6BB3VT-Calf Massager-SBV -KT-Exact/Phrase</t>
+          <t>Nexlev -Catch All-  Calf Massager -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -7905,19 +7905,19 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>6787.5</v>
+        <v>20614</v>
       </c>
       <c r="E29" t="n">
-        <v>278</v>
+        <v>108</v>
       </c>
       <c r="F29" t="n">
-        <v>3170.38</v>
+        <v>1652.333411823787</v>
       </c>
       <c r="G29" t="n">
-        <v>16415</v>
+        <v>8050.46</v>
       </c>
       <c r="H29" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -7929,28 +7929,28 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nexlev -B0DM6BB3VT-Calf Massager-SBV -KT-Exact/Phrase</t>
+          <t>Nexlev -Catch All-  Calf Massager -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B0FPGDVVCX</t>
+          <t>B0DVSZ2VVJ</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>6787.5</v>
+        <v>29176</v>
       </c>
       <c r="E30" t="n">
-        <v>278</v>
+        <v>153</v>
       </c>
       <c r="F30" t="n">
-        <v>3170.38</v>
+        <v>2338.642704600178</v>
       </c>
       <c r="G30" t="n">
-        <v>16415</v>
+        <v>11394.28</v>
       </c>
       <c r="H30" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -7967,23 +7967,23 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>B0DM6BB3VT</t>
+          <t>B0FPGDVVCX</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>23828.66666666667</v>
+        <v>21696</v>
       </c>
       <c r="E31" t="n">
-        <v>124.6666666666667</v>
+        <v>114</v>
       </c>
       <c r="F31" t="n">
-        <v>1910.003333333333</v>
+        <v>1739.033883576036</v>
       </c>
       <c r="G31" t="n">
-        <v>9305.873333333333</v>
+        <v>8472.879999999999</v>
       </c>
       <c r="H31" t="n">
-        <v>2.333333333333333</v>
+        <v>2</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -7995,28 +7995,28 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All-  Calf Massager -SB-KT-Exact/Phrase</t>
+          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B0DVSZ2VVJ</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>23828.66666666667</v>
+        <v>7578</v>
       </c>
       <c r="E32" t="n">
-        <v>124.6666666666667</v>
+        <v>53</v>
       </c>
       <c r="F32" t="n">
-        <v>1910.003333333333</v>
+        <v>673.4486152234572</v>
       </c>
       <c r="G32" t="n">
-        <v>9305.873333333333</v>
+        <v>4848.317074986327</v>
       </c>
       <c r="H32" t="n">
-        <v>2.333333333333333</v>
+        <v>3</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -8028,28 +8028,28 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All-  Calf Massager -SB-KT-Exact/Phrase</t>
+          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B0FPGDVVCX</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>23828.66666666667</v>
+        <v>15852</v>
       </c>
       <c r="E33" t="n">
-        <v>124.6666666666667</v>
+        <v>110</v>
       </c>
       <c r="F33" t="n">
-        <v>1910.003333333333</v>
+        <v>1408.781384776542</v>
       </c>
       <c r="G33" t="n">
-        <v>9305.873333333333</v>
+        <v>10142.15292501367</v>
       </c>
       <c r="H33" t="n">
-        <v>2.333333333333333</v>
+        <v>6</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -8061,28 +8061,28 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CDPMX152- Garment Steamer-SBV-KT-Phrase</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0CDPMX152</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>7810</v>
+        <v>12085</v>
       </c>
       <c r="E34" t="n">
-        <v>54.33333333333334</v>
+        <v>298</v>
       </c>
       <c r="F34" t="n">
-        <v>694.0766666666667</v>
+        <v>2642.996867321026</v>
       </c>
       <c r="G34" t="n">
-        <v>4996.823333333333</v>
+        <v>6811.931171459759</v>
       </c>
       <c r="H34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -8094,28 +8094,28 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CDPMX152- Garment Steamer-SBV-KT-Phrase</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B0DCGHKRXX</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>7810</v>
+        <v>3389</v>
       </c>
       <c r="E35" t="n">
-        <v>54.33333333333334</v>
+        <v>84</v>
       </c>
       <c r="F35" t="n">
-        <v>694.0766666666667</v>
+        <v>741.113132678974</v>
       </c>
       <c r="G35" t="n">
-        <v>4996.823333333333</v>
+        <v>1910.108828540242</v>
       </c>
       <c r="H35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -8127,28 +8127,28 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>7810</v>
+        <v>36362</v>
       </c>
       <c r="E36" t="n">
-        <v>54.33333333333334</v>
+        <v>718</v>
       </c>
       <c r="F36" t="n">
-        <v>694.0766666666667</v>
+        <v>9810.951566750373</v>
       </c>
       <c r="G36" t="n">
-        <v>4996.823333333333</v>
+        <v>66229.60306494836</v>
       </c>
       <c r="H36" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -8160,28 +8160,28 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPMX152- Garment Steamer-SBV-KT-Phrase</t>
+          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0CDPMX152</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>7737</v>
+        <v>3454</v>
       </c>
       <c r="E37" t="n">
-        <v>191</v>
+        <v>68</v>
       </c>
       <c r="F37" t="n">
-        <v>1692.055</v>
+        <v>945.6735656508489</v>
       </c>
       <c r="G37" t="n">
-        <v>4361.02</v>
+        <v>6101.360893909737</v>
       </c>
       <c r="H37" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -8193,28 +8193,28 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPMX152- Garment Steamer-SBV-KT-Phrase</t>
+          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>7737</v>
+        <v>6222</v>
       </c>
       <c r="E38" t="n">
-        <v>191</v>
+        <v>122</v>
       </c>
       <c r="F38" t="n">
-        <v>1692.055</v>
+        <v>1703.603977119995</v>
       </c>
       <c r="G38" t="n">
-        <v>4361.02</v>
+        <v>10991.42776350661</v>
       </c>
       <c r="H38" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -8231,23 +8231,23 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>52105</v>
+        <v>6067</v>
       </c>
       <c r="E39" t="n">
-        <v>1026</v>
+        <v>119</v>
       </c>
       <c r="F39" t="n">
-        <v>14121.23</v>
+        <v>1661.000890478784</v>
       </c>
       <c r="G39" t="n">
-        <v>94038.95000000001</v>
+        <v>10716.55827763531</v>
       </c>
       <c r="H39" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -8268,19 +8268,19 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1498</v>
+        <v>246</v>
       </c>
       <c r="E40" t="n">
-        <v>53.5</v>
+        <v>9</v>
       </c>
       <c r="F40" t="n">
-        <v>309.085</v>
+        <v>50.72585863994613</v>
       </c>
       <c r="G40" t="n">
-        <v>6377.615</v>
+        <v>1046.67</v>
       </c>
       <c r="H40" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -8301,19 +8301,19 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1498</v>
+        <v>2750</v>
       </c>
       <c r="E41" t="n">
-        <v>53.5</v>
+        <v>98</v>
       </c>
       <c r="F41" t="n">
-        <v>309.085</v>
+        <v>567.4441413600538</v>
       </c>
       <c r="G41" t="n">
-        <v>6377.615</v>
+        <v>11708.56</v>
       </c>
       <c r="H41" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -8330,23 +8330,23 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>20782</v>
+        <v>4902</v>
       </c>
       <c r="E42" t="n">
-        <v>615</v>
+        <v>145</v>
       </c>
       <c r="F42" t="n">
-        <v>10078.23</v>
+        <v>2377.134810595717</v>
       </c>
       <c r="G42" t="n">
-        <v>40961.84</v>
+        <v>9661.598888897362</v>
       </c>
       <c r="H42" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -8358,28 +8358,28 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>6397.666666666667</v>
+        <v>12086</v>
       </c>
       <c r="E43" t="n">
-        <v>37</v>
+        <v>358</v>
       </c>
       <c r="F43" t="n">
-        <v>536.87</v>
+        <v>5861.088593593876</v>
       </c>
       <c r="G43" t="n">
-        <v>1694.35</v>
+        <v>23821.73984882438</v>
       </c>
       <c r="H43" t="n">
-        <v>0.3333333333333333</v>
+        <v>6</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -8391,28 +8391,28 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DTK4FY1G</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>6397.666666666667</v>
+        <v>1847</v>
       </c>
       <c r="E44" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="F44" t="n">
-        <v>536.87</v>
+        <v>895.7312891725613</v>
       </c>
       <c r="G44" t="n">
-        <v>1694.35</v>
+        <v>3640.599763061588</v>
       </c>
       <c r="H44" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -8433,19 +8433,19 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>6397.666666666667</v>
+        <v>1947</v>
       </c>
       <c r="E45" t="n">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="F45" t="n">
-        <v>536.87</v>
+        <v>944.2753066378452</v>
       </c>
       <c r="G45" t="n">
-        <v>1694.35</v>
+        <v>3837.901499216664</v>
       </c>
       <c r="H45" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -8457,25 +8457,25 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>26698</v>
+        <v>19193</v>
       </c>
       <c r="E46" t="n">
-        <v>62</v>
+        <v>111</v>
       </c>
       <c r="F46" t="n">
-        <v>614.015</v>
+        <v>1610.61</v>
       </c>
       <c r="G46" t="n">
-        <v>2664.405</v>
+        <v>5083.05</v>
       </c>
       <c r="H46" t="n">
         <v>1</v>
@@ -8495,25 +8495,58 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>26698</v>
+        <v>24618</v>
       </c>
       <c r="E47" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="F47" t="n">
-        <v>614.015</v>
+        <v>566.1675952792463</v>
       </c>
       <c r="G47" t="n">
-        <v>2664.405</v>
+        <v>2456.78</v>
       </c>
       <c r="H47" t="n">
         <v>1</v>
       </c>
       <c r="I47" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>28778</v>
+      </c>
+      <c r="E48" t="n">
+        <v>67</v>
+      </c>
+      <c r="F48" t="n">
+        <v>661.8624047207538</v>
+      </c>
+      <c r="G48" t="n">
+        <v>2872.03</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" t="inlineStr">
         <is>
           <t>Nexlev</t>
         </is>

--- a/data/ams_weekly_data/Nexlev/ads_report_week18.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week18.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="SD" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="SB" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SB" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
